--- a/be/src/mindbody/fixtures/reports/Clients/15 Visits Remaining/15 Visits Remaining - Detail.xlsx
+++ b/be/src/mindbody/fixtures/reports/Clients/15 Visits Remaining/15 Visits Remaining - Detail.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">Client ID</t>
   </si>
@@ -212,6 +212,84 @@
   </si>
   <si>
     <t xml:space="preserve">Instructor, Ivy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rick.roe@example.test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doe, Jane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop - Twin (Deposit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/1/2090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91234567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jane.doe@example.test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doe, Jane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop - Upgrade to Single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/1/2090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91234567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jane.doe@example.test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roe, Rick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handstand Workshop - Twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/9/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/1/2090</t>
   </si>
   <si>
     <t xml:space="preserve">rick.roe@example.test</t>
@@ -743,312 +821,432 @@
         <v>75</v>
       </c>
       <c r="G7">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
         <v>76</v>
       </c>
-      <c r="J7" t="s">
+      <c r="P7" t="s">
         <v>77</v>
       </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="S7" t="s">
         <v>78</v>
-      </c>
-      <c r="S7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>83</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>84</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8">
+        <v>250</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
         <v>85</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="P8" t="s">
         <v>86</v>
       </c>
-      <c r="J8" t="s">
+      <c r="S8" t="s">
         <v>87</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>88</v>
-      </c>
-      <c r="S8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
         <v>90</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>91</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>92</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>93</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9">
+        <v>500</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="P9" t="s">
         <v>94</v>
       </c>
-      <c r="F9" t="s">
+      <c r="S9" t="s">
         <v>95</v>
-      </c>
-      <c r="G9">
-        <v>120</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" t="s">
-        <v>97</v>
-      </c>
-      <c r="S9" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
         <v>99</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>100</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>101</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10">
+        <v>1200</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="E10" t="s">
+      <c r="J10" t="s">
         <v>103</v>
       </c>
-      <c r="F10" t="s">
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="P10" t="s">
         <v>104</v>
       </c>
-      <c r="G10">
-        <v>60</v>
-      </c>
-      <c r="H10">
-        <v>99999</v>
-      </c>
-      <c r="K10">
-        <v>99999</v>
-      </c>
-      <c r="L10">
-        <v>99999</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="S10" t="s">
         <v>105</v>
-      </c>
-      <c r="P10" t="s">
-        <v>106</v>
-      </c>
-      <c r="S10" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
         <v>108</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>109</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>110</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>111</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
         <v>112</v>
       </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>113</v>
       </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
         <v>114</v>
       </c>
-      <c r="J11" t="s">
+      <c r="S11" t="s">
         <v>115</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="P11" t="s">
-        <v>116</v>
-      </c>
-      <c r="S11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" t="s">
         <v>118</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>119</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>120</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>121</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12">
+        <v>120</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
         <v>122</v>
       </c>
-      <c r="F12" t="s">
+      <c r="P12" t="s">
         <v>123</v>
       </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="S12" t="s">
         <v>124</v>
-      </c>
-      <c r="S12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
         <v>126</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>127</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>128</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>129</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>130</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13">
+        <v>60</v>
+      </c>
+      <c r="H13">
+        <v>99999</v>
+      </c>
+      <c r="K13">
+        <v>99999</v>
+      </c>
+      <c r="L13">
+        <v>99999</v>
+      </c>
+      <c r="N13" t="s">
         <v>131</v>
       </c>
-      <c r="G13">
-        <v>250</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="P13" t="s">
         <v>132</v>
       </c>
-      <c r="J13" t="s">
+      <c r="S13" t="s">
         <v>133</v>
-      </c>
-      <c r="K13">
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <v>3</v>
-      </c>
-      <c r="P13" t="s">
-        <v>134</v>
-      </c>
-      <c r="S13" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
         <v>136</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>137</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>138</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>139</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
         <v>140</v>
       </c>
-      <c r="G14">
+      <c r="J14" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>142</v>
+      </c>
+      <c r="S14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>150</v>
+      </c>
+      <c r="S15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16">
+        <v>250</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J16" t="s">
+        <v>159</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="P16" t="s">
+        <v>160</v>
+      </c>
+      <c r="S16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17">
         <v>450</v>
       </c>
-      <c r="H14">
+      <c r="H17">
         <v>4</v>
       </c>
-      <c r="K14">
+      <c r="K17">
         <v>20</v>
       </c>
-      <c r="L14">
+      <c r="L17">
         <v>4</v>
       </c>
-      <c r="S14" t="s">
-        <v>141</v>
+      <c r="S17" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
